--- a/backend/tools/balance_pipeline/balance.xlsx
+++ b/backend/tools/balance_pipeline/balance.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet name="Scalars" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Weapons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ArmorRollRanges" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ArmorMarketValues" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="VendingMachineUpgradeCosts" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MergeGridUnlockCosts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="WeaponLevelMultipliers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ArmorRollRanges" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ArmorMarketValues" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="VendingMachineUpgradeCosts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MergeGridUnlockCosts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CharacterSlotUnlockCosts" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,12 +420,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -446,622 +448,622 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Weapons.TierDamageMultiplier</t>
+          <t>Weapons.MaxTier</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.6</v>
+        <v>15</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>머지 1회(동일 무기 2개 결합)당 데미지 성장 배율</t>
+          <t>무기 최대 레벨(현재 15: 10레벨이 실질 엔드스펙, 15레벨은 극단적 하이롤)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Weapons.MaxTier</t>
+          <t>Weapons.SkillBonusAtLevel5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>0.15</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>무기 최대 티어</t>
+          <t>무기 스킬 마일스톤 Lv.5 도달 시 가산 전투력 보너스(근사 스킬 반영)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Armor.DodgeClampMax</t>
+          <t>Weapons.SkillBonusAtLevel10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>회피율 상한(0~1)</t>
+          <t>무기 스킬 마일스톤 Lv.10 도달 시 가산 전투력 보너스(스택 누적)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VendingMachine.BaseHealth</t>
+          <t>Weapons.SkillBonusAtLevel15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>300</v>
+        <v>0.65</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>자판기 기본 체력</t>
+          <t>무기 스킬 마일스톤 Lv.15 도달 시 가산 전투력 보너스(스택 누적)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VendingMachine.MaxUpgradeLevel</t>
+          <t>Armor.DodgeClampMax</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>공격/방어 업그레이드 최대 레벨</t>
+          <t>회피율 상한(0~1)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VendingMachine.WeaponRollCost</t>
+          <t>VendingMachine.MaxUpgradeLevel</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>무기 뽑기 1회 골드 비용</t>
+          <t>공격/방어 업그레이드 최대 레벨</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VendingMachine.ArmorRollCost</t>
+          <t>VendingMachine.WeaponRollCost</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>방어구 뽑기 1회 골드 비용</t>
+          <t>무기 뽑기 1회 골드 비용</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VendingMachine.Tier2ChanceBase</t>
+          <t>VendingMachine.ArmorRollCost</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>공격 업그레이드 Lv1 기준 2티어 무기 등장 확률</t>
+          <t>방어구 뽑기 1회 골드 비용</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VendingMachine.Tier2ChancePerLevel</t>
+          <t>VendingMachine.Tier2ChanceBase</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>공격 업그레이드 레벨당 2티어 확률 증가량</t>
+          <t>공격 업그레이드 Lv1 기준 2티어 무기 등장 확률</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VendingMachine.LegendaryChanceBase</t>
+          <t>VendingMachine.Tier2ChancePerLevel</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>방어 업그레이드 Lv1 기준 전설 등급 확률</t>
+          <t>공격 업그레이드 레벨당 2티어 확률 증가량</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VendingMachine.LegendaryChancePerLevel</t>
+          <t>VendingMachine.LegendaryChanceBase</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>방어 업그레이드 레벨당 전설 확률 증가량</t>
+          <t>방어 업그레이드 Lv1 기준 전설 등급 확률</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VendingMachine.EpicChanceBase</t>
+          <t>VendingMachine.LegendaryChancePerLevel</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>방어 업그레이드 Lv1 기준 영웅 등급 확률</t>
+          <t>방어 업그레이드 레벨당 전설 확률 증가량</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VendingMachine.EpicChancePerLevel</t>
+          <t>VendingMachine.EpicChanceBase</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>방어 업그레이드 레벨당 영웅 확률 증가량</t>
+          <t>방어 업그레이드 Lv1 기준 영웅 등급 확률</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VendingMachine.RareChanceBase</t>
+          <t>VendingMachine.EpicChancePerLevel</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>방어 업그레이드 Lv1 기준 희귀 등급 확률</t>
+          <t>방어 업그레이드 레벨당 영웅 확률 증가량</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VendingMachine.RareChancePerLevel</t>
+          <t>VendingMachine.RareChanceBase</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>방어 업그레이드 레벨당 희귀 확률 증가량</t>
+          <t>방어 업그레이드 Lv1 기준 희귀 등급 확률</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Wave.ScaleBase</t>
+          <t>VendingMachine.RareChancePerLevel</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>웨이브 스탯 스케일 기준값(1스테이지)</t>
+          <t>방어 업그레이드 레벨당 희귀 확률 증가량</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Wave.ScalePerStage</t>
+          <t>Wave.ScaleBase</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.07000000000000001</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>스테이지당 스탯 스케일 증가량</t>
+          <t>웨이브 스탯 스케일 기준값(1스테이지)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wave.MobCountBase</t>
+          <t>Wave.ScalePerStage</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>0.035</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>일반 몹 기본 마리 수</t>
+          <t>스테이지당 스탯 스케일 증가량</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wave.MobCountStageDivisor</t>
+          <t>Wave.MobCountBase</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>몹 수 = MobCountBase + stage / 이 값</t>
+          <t>일반 몹 기본 마리 수</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wave.MobBaseHealth</t>
+          <t>Wave.MobCountStageDivisor</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>일반 몹 기본 체력(스케일 적용 전)</t>
+          <t>몹 수 = MobCountBase + stage / 이 값</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wave.MobBaseDamage</t>
+          <t>Wave.MobBaseHealth</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>일반 몹 기본 공격력(스케일 적용 전)</t>
+          <t>일반 몹 기본 체력(스케일 적용 전)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Wave.MobApsMin</t>
+          <t>Wave.MobBaseDamage</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>일반 몹 초당 공격 횟수 최소값</t>
+          <t>일반 몹 기본 공격력(스케일 적용 전)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wave.MobApsRandomRange</t>
+          <t>Wave.MobApsMin</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>일반 몹 초당 공격 횟수 랜덤 폭(+0~이 값)</t>
+          <t>일반 몹 초당 공격 횟수 최소값</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wave.MobGoldBase</t>
+          <t>Wave.MobApsRandomRange</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>일반 몹 처치 골드 기본값</t>
+          <t>일반 몹 초당 공격 횟수 랜덤 폭(+0~이 값)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Wave.MobGoldStageDivisor</t>
+          <t>Wave.MobGoldBase</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>몹 골드 = MobGoldBase + stage / 이 값</t>
+          <t>일반 몹 처치 골드 기본값</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wave.MidBossHealth</t>
+          <t>Wave.MobGoldStageDivisor</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>중간 보스 기본 체력(스케일 적용 전)</t>
+          <t>몹 골드 = MobGoldBase + stage / 이 값</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wave.MidBossDamage</t>
+          <t>Wave.MidBossHealth</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>220</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>중간 보스 기본 공격력(스케일 적용 전)</t>
+          <t>중간 보스 기본 체력(스케일 적용 전)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wave.MidBossAps</t>
+          <t>Wave.MidBossDamage</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>중간 보스 초당 공격 횟수</t>
+          <t>중간 보스 기본 공격력(스케일 적용 전)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Wave.MidBossGoldBase</t>
+          <t>Wave.MidBossAps</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>40</v>
+        <v>0.6</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>중간 보스 처치 골드 기본값</t>
+          <t>중간 보스 초당 공격 횟수</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Wave.MidBossGoldPerStage</t>
+          <t>Wave.MidBossGoldBase</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>중간 보스 골드 스테이지당 증가량</t>
+          <t>중간 보스 처치 골드 기본값</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Wave.BigBossHealth</t>
+          <t>Wave.MidBossGoldPerStage</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>대형 보스 기본 체력(스케일 적용 전)</t>
+          <t>중간 보스 골드 스테이지당 증가량</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wave.BigBossDamage</t>
+          <t>Wave.BigBossHealth</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18</v>
+        <v>600</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>대형 보스 기본 공격력(스케일 적용 전)</t>
+          <t>대형 보스 기본 체력(스케일 적용 전)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wave.BigBossAps</t>
+          <t>Wave.BigBossDamage</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5</v>
+        <v>18</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>대형 보스 초당 공격 횟수</t>
+          <t>대형 보스 기본 공격력(스케일 적용 전)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wave.BigBossGoldBase</t>
+          <t>Wave.BigBossAps</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>120</v>
+        <v>0.5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>대형 보스 처치 골드 기본값</t>
+          <t>대형 보스 초당 공격 횟수</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wave.BigBossGoldPerStage</t>
+          <t>Wave.BigBossGoldBase</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>대형 보스 골드 스테이지당 증가량</t>
+          <t>대형 보스 처치 골드 기본값</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MetaProgression.MaxLevel</t>
+          <t>Wave.BigBossGoldPerStage</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>영혼 스킬트리 항목별 최대 레벨</t>
+          <t>대형 보스 골드 스테이지당 증가량</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MetaProgression.LevelCostBase</t>
+          <t>MetaProgression.MaxLevel</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>레벨업 비용 기본값</t>
+          <t>영혼 스킬트리 항목별 최대 레벨</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MetaProgression.LevelCostPerLevel</t>
+          <t>MetaProgression.LevelCostBase</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>레벨업 비용 = Base + 현재레벨 * 이 값</t>
+          <t>레벨업 비용 기본값</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MetaProgression.RetireSpeedPerLevel</t>
+          <t>MetaProgression.LevelCostPerLevel</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.15</v>
+        <v>30</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>리타이어 타이머 진행 속도 레벨당 증가율</t>
+          <t>레벨업 비용 = Base + 현재레벨 * 이 값</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MetaProgression.FirstRollTierBoostPerLevel</t>
+          <t>MetaProgression.RetireSpeedPerLevel</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>런 시작 첫 뽑기 2티어 확정 확률 레벨당 증가량</t>
+          <t>리타이어 타이머 진행 속도 레벨당 증가율</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MetaProgression.BaseHealthBonusPerLevel</t>
+          <t>MetaProgression.FirstRollTierBoostPerLevel</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>전 캐릭터 기본 체력 가산치 레벨당 증가량</t>
+          <t>런 시작 첫 뽑기 2티어 확정 확률 레벨당 증가량</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Currency.WeaponMarketValueTierBase</t>
+          <t>MetaProgression.BaseHealthBonusPerLevel</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1069,44 +1071,44 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>무기 시세 = 이 값 * 2^(티어-1)</t>
+          <t>전 캐릭터 기본 체력 가산치 레벨당 증가량</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Currency.SellRefundRatio</t>
+          <t>Currency.WeaponMarketValueTierBase</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>장비 판매 환급 비율(0~1)</t>
+          <t>무기 시세 = 이 값 * 2^(티어-1)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>StageLoop.MaxStage</t>
+          <t>Currency.SellRefundRatio</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>런 클리어 목표 스테이지 수</t>
+          <t>장비 판매 환급 비율(0~1)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>StageLoop.VictoryGoldBase</t>
+          <t>StageLoop.MaxStage</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1114,187 +1116,217 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>스테이지 클리어 골드 보상 기본값</t>
+          <t>런 클리어 목표 스테이지 수</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>StageLoop.VictoryGoldPerStage</t>
+          <t>StageLoop.VictoryGoldBase</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>골드 보상 스테이지당 증가량</t>
+          <t>스테이지 클리어 골드 보상 기본값</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>StageLoop.VictoryGemsDefault</t>
+          <t>StageLoop.VictoryGoldPerStage</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>평시 스테이지 클리어 보석 보상</t>
+          <t>골드 보상 스테이지당 증가량</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>StageLoop.VictoryGemsMilestone</t>
+          <t>StageLoop.VictorySoulsBase</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>마일스톤 스테이지 클리어 보석 보상</t>
+          <t>스테이지 클리어 영혼 보상 기본값</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>StageLoop.VictoryGemsMilestoneInterval</t>
+          <t>StageLoop.VictorySoulsStageDivisor</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>보석 마일스톤 간격(스테이지)</t>
+          <t>영혼 보상 = Base + stage / 이 값</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>StageLoop.VictorySoulsBase</t>
+          <t>Character.BaseHealth</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>스테이지 클리어 영혼 보상 기본값</t>
+          <t>캐릭터(빈 껍데기) 기본 체력</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>StageLoop.VictorySoulsStageDivisor</t>
+          <t>Character.RetireDurationSeconds</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>영혼 보상 = Base + stage / 이 값</t>
+          <t>리타이어 지속 시간(초)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Character.BaseHealth</t>
+          <t>Combat.ElementAdvantageMultiplier</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>70</v>
+        <v>1.5</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>캐릭터(빈 껍데기) 기본 체력</t>
+          <t>속성 상성 유리 시 데미지 배율</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Character.RetireDurationSeconds</t>
+          <t>Combat.ElementDisadvantageMultiplier</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>리타이어 지속 시간(초)</t>
+          <t>속성 상성 불리 시 데미지 배율</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Combat.ElementAdvantageMultiplier</t>
+          <t>MergeGrid.TotalCells</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.5</v>
+        <v>16</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>속성 상성 유리 시 데미지 배율</t>
+          <t>머지 그리드 총 칸 수(무기+방어구 공유)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Combat.ElementDisadvantageMultiplier</t>
+          <t>MergeGrid.CellsPerUnlock</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>속성 상성 불리 시 데미지 배율</t>
+          <t>그리드 해금 단위(칸)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MergeGrid.TotalCells</t>
+          <t>Rune.NormalStageDropChance</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>16</v>
+        <v>0.08</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>머지 그리드 총 칸 수</t>
+          <t>일반 스테이지 클리어 시 룬 드롭 확률</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MergeGrid.CellsPerUnlock</t>
+          <t>Rune.BossStageDropChance</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>그리드 해금 단위(칸)</t>
+          <t>중간/대형 보스 스테이지 클리어 시 룬 드롭 확률</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CharacterSlots.StartingSlots</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>런 시작 시 기본 캐릭터 인원</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CharacterSlots.MaxSlots</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>골드로 해금 가능한 최대 캐릭터 인원</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1525,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1502,6 +1534,156 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Multiplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1661,7 +1843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1731,7 +1913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1793,7 +1975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1845,4 +2027,66 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>GoldCost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/backend/tools/balance_pipeline/balance.xlsx
+++ b/backend/tools/balance_pipeline/balance.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Scalars" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Weapons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="WeaponLevelMultipliers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ArmorRollRanges" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ArmorMarketValues" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="VendingMachineUpgradeCosts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="MergeGridUnlockCosts" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="CharacterSlotUnlockCosts" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalars" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponLevelMultipliers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorRollRanges" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorMarketValues" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VendingMachineUpgradeCosts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MergeGridUnlockCosts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterSlotUnlockCosts" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,10 +420,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="47" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1273,60 +1273,405 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rune.NormalStageDropChance</t>
+          <t>CharacterSlots.StartingSlots</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>일반 스테이지 클리어 시 룬 드롭 확률</t>
+          <t>런 시작 시 기본 캐릭터 인원</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rune.BossStageDropChance</t>
+          <t>CharacterSlots.MaxSlots</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>중간/대형 보스 스테이지 클리어 시 룬 드롭 확률</t>
+          <t>골드로 해금 가능한 최대 캐릭터 인원</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CharacterSlots.StartingSlots</t>
+          <t>ElementEffects.FireBurnDamagePerSecond</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>런 시작 시 기본 캐릭터 인원</t>
+          <t>불: 화상 초당 도트 데미지</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CharacterSlots.MaxSlots</t>
+          <t>ElementEffects.FireBurnDurationSeconds</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>불: 화상 지속시간(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ElementEffects.FireSplashRatio</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>불: 다른 생존 몬스터에게 전파되는 화상 피해 비율(범위 도트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ElementEffects.IceSlowRatio</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>얼음: 피격 대상 공격속도 감소율(0~1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ElementEffects.IceSlowDurationSeconds</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>얼음: 둔화 지속시간(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ElementEffects.PoisonDamagePerStackPerSecond</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>독: 중첩 1개당 초당 도트 데미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ElementEffects.PoisonDurationSeconds</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
         <v>5</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>골드로 해금 가능한 최대 캐릭터 인원</t>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>독: 중첩 유지/갱신 지속시간(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ElementEffects.PoisonMaxStacks</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>독: 최대 중첩 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ElementEffects.LightningChainDamageRatio</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>전기: 원 피해량 대비 다른 몬스터 1명에게 전이되는 피해 비율</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ElementEffects.HolyLifestealRatio</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>빛: 원 피해량 대비 공격자 회복 비율(흡혈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ElementEffects.DarkBonusDamageRatio</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>어둠: 원 피해량 대비 같은 대상에게 추가되는 즉시 피해 비율</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.RegularGoldOption</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>30</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>기본 스테이지 선택보상 ①: 골드</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.RegularAttackBoost</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>기본 스테이지 선택보상 ②: 공격력 영구증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.RegularHealthBoost</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>기본 스테이지 선택보상 ②: 체력 영구증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.RegularBoxRuneChance</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>기본 스테이지 선택보상 ③ 상자: 룬 확률(나머지는 유물)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.MidBossBaseSoulsBonus</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>5</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>중간보스(ST 5·15·25) 기본보상에 추가되는 영혼</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.MidBossGoldOption</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>80</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>중간보스 선택보상 ①: 골드(강화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.MidBossAttackBoost</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>8</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>중간보스 선택보상 ②: 공격력 영구증가(강화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.MidBossHealthBoost</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>11</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>중간보스 선택보상 ②: 체력 영구증가(강화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.MidBossBoxRuneChance</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>중간보스 선택보상 ③ 상자: 룬 확률(나머지는 유물)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.BossBaseSoulsBonus</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>12</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>보스(ST 10·20·30) 기본보상에 추가되는 영혼</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.BossGoldOption</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>150</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>보스 선택보상 ①: 골드(더 강화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.BossAttackBoost</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>15</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>보스 선택보상 ②: 공격력 영구증가(더 강화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.BossHealthBoost</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>20</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>보스 선택보상 ②: 체력 영구증가(더 강화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>StageRewardChoice.BossBoxRuneChance</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>보스 선택보상 ③ 상자: 룬 확률(나머지는 유물)</t>
         </is>
       </c>
     </row>

--- a/backend/tools/balance_pipeline/balance.xlsx
+++ b/backend/tools/balance_pipeline/balance.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>11</v>
+        <v>1.4</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="5">
@@ -2165,22 +2165,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C5" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.12</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.16</v>
       </c>
     </row>
   </sheetData>
